--- a/compliance_master_dataset.xlsx
+++ b/compliance_master_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,55 +429,50 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>matching_text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>client_dob</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>hit_dob</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>client_country</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>client_city</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>hit_country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>hit_city</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>screening_type</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>hit_type</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>decision_reason</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>decision_reason</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>thinking</t>
         </is>
@@ -486,1890 +481,8284 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Al-Saud, Faisal bin Abdulaziz</t>
+          <t>Garcia, Maria Elena</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Al-Saud, Faisal bin Abdulaziz</t>
+          <t>GARCIA, Maria Elena</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1975-05-20</t>
+          <t>Garcia ~ GARCIA | Maria ~ MARIA | Elena ~ ELENA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1975-05-20</t>
+          <t>1988-03-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>22 March 1988</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>España</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J2" t="b">
         <v>1</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Exact name, DOB, and geography match.</t>
+          <t>Exact name match with matching DOB and identical geography.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ivanov, Dmitri</t>
+          <t>Ivanov, Aleksandr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ivanov, Dmitri</t>
+          <t>ИВАНОВ, Александр</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1980-11-12</t>
+          <t>Ivanov ~ ИВАНОВ | Aleksandr ~ Александр</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1981-01-05</t>
+          <t>22nd July 1985</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>22 July 1985</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Moscow</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Moscow</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Exact name match with DOB variance under 1 year and matching geography.</t>
+          <t>Cross-script transliteration yields an exact name match with aligned DOB and geography.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chen, Wei</t>
+          <t>Patel, Priya</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chen, Wei</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>PATEL, PRIYA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Patel ~ PATEL | Priya ~ PRIYA</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1965-08-22</t>
+          <t>15/08/1995</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>August 15, 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
         <v>1</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_MISSING_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Client DOB missing; name and geography match exactly.</t>
+          <t>Exact name match with matching DOB formats and fully verified country and city geography.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Müller, Hans</t>
+          <t>Al-Assad, Bashar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Müller, Hans</t>
+          <t>ASSAD, Batyr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1955-03-10</t>
+          <t>Al-Assad ~ ASSAD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1955-03-10</t>
+          <t>1965-09-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>1965-09-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Exact name and DOB match; hit city is missing but country matches.</t>
+          <t>Engine over-fired on the stripped family name prefix while given names do not match.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Santos, Maria</t>
+          <t>Smith, Adelaide Jane</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>SMITH, Robert</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1992-07-14</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15-04-1982</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>1982-04-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>embargo</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>EMBARGO_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Embargo hit type with matching country (Iran).</t>
+          <t>DOB matches and geography matches, but names belong to different individuals due to common surname over-match.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Okonkwo, Chidi</t>
+          <t>John, Robert</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Okonkwo, Chidi</t>
+          <t>IVAN, Robert</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1988-12-01</t>
+          <t>Robert ~ ROBERT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1988-11-15</t>
+          <t>1985-06-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>1985-06-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>London</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Exact name match with acceptable DOB variance and matching geography.</t>
+          <t>Shared secondary name Robert triggered the engine, but primary given names are completely different.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zheng, Li</t>
+          <t>Petrov, Dmitri</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Li, Zheng</t>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1988-11-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>1970-01-01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1970-01-01</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NAME_MISMATCH</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Token order mismatch (Zheng, Li vs Li, Zheng).</t>
+          <t>Name elements cross transliteration scripts, but a major DOB disparity of over 18 years triggers a mismatch.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Garcia, Sofia</t>
+          <t>Silva, Joao</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garcia, Sofia</t>
+          <t>SILVA, Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1995-06-15</t>
+          <t>Silva ~ SILVA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1980-06-15</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DOB_MISMATCH_OR_INVALID</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Significant DOB difference exceeding 1 year.</t>
+          <t>Names and DOBs match, but client and hit reside in completely different countries.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kim, Min-jun</t>
+          <t>O'Brien, Siobhan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>BRIEN, Michael</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1985-04-04</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Brien ~ BRIEN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1978-04-04</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>1978-04-04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>North Korea</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>embargo</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EMBARGO_WILDCARD_HIT</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Embargo hit for North Korea does not match client country South Korea.</t>
+          <t>Engine matched on an apostrophe-split substring of the surname, but given names mismatch.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dubois, Marc</t>
+          <t>Al-Assad, Bashar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dubois, Marc</t>
+          <t>ASSAD, Batyr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1972-09-30</t>
+          <t>Al-Assad ~ ASSAD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1972-09-30</t>
+          <t>1965-09-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>1965-09-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Damascus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>GEOGRAPHIC_MISMATCH</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Name and DOB match, but client is in France and hit is in Canada.</t>
+          <t>Name matches via prefix stripping and DOB is identical, but countries do not align resulting in geographic mismatch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Al-Sayed, Omar</t>
+          <t>Garcia, Maria Elena</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Al-Sayed, Omar</t>
+          <t>GARCIA, Maria Elena</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1975-11-20</t>
+          <t>Garcia ~ GARCIA | Maria ~ Maria | Elena ~ Elena</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1975-11-20</t>
+          <t>14/03/1978</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>15-03-1978</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>España</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
         <v>1</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Exact name, DOB, and country match.</t>
+          <t>DOB difference is within acceptable tolerance, geography matches, and names are an exact structured match.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chen, Wei</t>
+          <t>Smith, Jane Adelaide</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>SMITH, Robert</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1988-05-12</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>15/04/1982</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>1982-04-20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyongyang</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Embargoes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>embargo</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>EMBARGO_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Embargo hit type with matching client country.</t>
+          <t>DOB matches and geography matches, but names belong to completely different individuals sharing a common surname.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Schmidt, Hans-Dieter</t>
+          <t>Patel, Dipak</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Schmidt, Hans-Dieter</t>
+          <t>PATEL, Dinesh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1962-08-01</t>
+          <t>Patel ~ PATEL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1962-07-28</t>
+          <t>1969-07-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>1969-07-14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Exact name match with acceptable DOB variance (&lt; 1 year) and matching geography.</t>
+          <t>Common surname over-match triggered the engine, but given names clearly do not match.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Silva, Maria Fernanda</t>
+          <t>Cruz-Ramirez, Elena</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Silva, Maria Fernanda</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>RAMIREZ, Jorge</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ramirez ~ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1988-10-30</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>1988-10-30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_MISSING_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Exact name and country match; DOB missing for both, bypassing DOB check.</t>
+          <t>DOB and name tokens align, but the country and city of residence represent a profound geographic contradiction.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ivanov, Dmitri</t>
+          <t>Ivanov, Dmitry</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ivanov, Dmitri</t>
+          <t>ИВАНОВ, ДМИТРИЙ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1980-01-15</t>
+          <t>Ivanov ~ ИВАНОВ | Dmitry ~ ДМИТРИЙ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1980-01-15</t>
+          <t>1975.05.20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>20.05.1975</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Moscow</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
+      <c r="J16" t="b">
         <v>1</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Exact name and DOB match; hit city is missing but country matches.</t>
+          <t>DOB matches within acceptable tolerances and geography validates successfully across script transliterations. Exact name match confirmed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nkosi, Zanele</t>
+          <t>Al-Mansoor, Tariq</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nkosi, Zanele</t>
+          <t>MANSOOR, Tariq bin Ziyad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1992-03-10</t>
+          <t>Mansoor ~ MANSOOR | Tariq ~ Tariq</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1992-03-10</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Dubai, AE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Johannesburg</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Full match across name, DOB, and geography.</t>
+          <t>Geographies match and name tokens overlap, but there is a major 12-year disparity in DOBs.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tanaka, Kenji</t>
+          <t>Müller, Hans</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kenji, Tanaka</t>
+          <t>MUELLER, Josef</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1970-06-20</t>
+          <t>Müller ~ MUELLER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1970-06-20</t>
+          <t>15/04/78</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>15-04-1978</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>München</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NAME_MISMATCH</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Token order mismatch (Tanaka, Kenji vs Kenji, Tanaka).</t>
+          <t>DOB matches and geography checks pass, but given names are entirely different. Fired on common surname root.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dubois, Marc</t>
+          <t>Wong, Li Wei</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dubois, Marc</t>
+          <t>WONG, Wei</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1985-12-01</t>
+          <t>Wong ~ WONG | Wei ~ Wei</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1970-12-01</t>
+          <t>1992-01-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>1992-01-15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>DOB_MISMATCH_OR_INVALID</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Major DOB disparity (15 years) triggers failure.</t>
+          <t>Names match via partial CJK token overlap, but conflicting countries cause a geographic mismatch.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O'Connor, Siobhan</t>
+          <t>Tanaka, Hiroshi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>O'Connor, Siobhan</t>
+          <t>TANAKA, Hiroshi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1995-07-07</t>
+          <t>Tanaka ~ TANAKA | Hiroshi ~ Hiroshi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1995-07-07</t>
+          <t>12 April 1970</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>1970-04-12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dublin</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>GEOGRAPHIC_MISMATCH</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Name and DOB match, but client country (Ireland) differs from hit country (USA).</t>
+          <t>Exact name match with compatible DOB representations; hit_city unavailable - bypassing geography.  [auto-null: client_city]  [auto-null: hit_country]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lee, Min-ho</t>
+          <t>Al-Assad, Bashar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>ASSAD, Batyr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1982-02-14</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>1960-01-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Damascus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Embargoes</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>embargo</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
+          <t>Aleppo</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>EMBARGO_WILDCARD_HIT</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Embargo hit for Iran, but client is located in South Korea.</t>
+          <t>Severe date of birth disparity exceeding the 1 year tolerance threshold.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Al-Sayed, Omar</t>
+          <t>García, Ana María</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Al-Sayed, Omar</t>
+          <t>GARCIA, Luis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1975-06-12</t>
+          <t>García ~ GARCIA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1975-06-12</t>
+          <t>05/14/1982</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>05/14/1982</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>1</v>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Exact name, DOB, and country match.</t>
+          <t>Shared common surname García triggers engine, but given names are completely different.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chen, Wei</t>
+          <t>García, Ana María</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>GARCIA, Luis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1988-11-20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>García ~ GARCIA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1992-03-14</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>1992-03-14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pyongyang</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Embargoes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>embargo</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>1</v>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>EMBARGO_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Embargo hit type with matching client country.</t>
+          <t>Accent-stripped surname matches the engine, but client and hit countries represent distinct jurisdictions.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schmidt, Hans, Jürgen</t>
+          <t>Smyth, James</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Schmidt, Hans, Jürgen</t>
+          <t>SMITH, James</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1962-03-15</t>
+          <t>Smyth ~ SMITH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1962-03-20</t>
+          <t>15/04/75</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>1975-04-15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>1</v>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Exact name match and DOB variance is less than one year.</t>
+          <t>Phonetic spelling variant between Smyth and SMITH triggers an engine match for different individuals.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oliveira, Maria</t>
+          <t>Srivastava, Rajesh</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Oliveira, Maria</t>
+          <t>SRIVASTAVA, Rajesh</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1992-08-01</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Srivastava ~ SRIVASTAVA | Rajesh ~ Rajesh</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>05.11.1980</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>05/11/1980</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>1</v>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_MISSING_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Exact name and country match; hit DOB is missing, proceeding to name check.</t>
+          <t>Names and DOBs match correctly, but conflicting country and city values trigger a geographic mismatch.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tanaka, Kenji</t>
+          <t>Smith, Jane Adelaide</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tanaka, Kenji</t>
+          <t>SMITH, Robert</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1980-01-10</t>
+          <t>Smith ~ SMITH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1980-01-10</t>
+          <t>15/04/1982</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>12-09-1975</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>1</v>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Exact name and DOB match; hit city is missing, proceeding to match.</t>
+          <t>Shared common surname Smith triggered the engine, but given names and individuals do not match.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dubois, Claire</t>
+          <t>O'Brien, Siobhan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dubois, Claire</t>
+          <t>BRIEN, Michael</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1970-12-25</t>
+          <t>Brien ~ BRIEN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1971-01-05</t>
+          <t>1981-12-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>1981-12-02</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Exact name match with DOB difference of 11 days (under 1 year).</t>
+          <t>Engine over-fires on the split surname Brien, but given names and distinct individuals prove name mismatch.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ivanov, Dmitry</t>
+          <t>Al-Assad, Bashar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dmitry, Ivanov</t>
+          <t>ASSAD, Batyr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1985-05-05</t>
+          <t>Al-Assad ~ ASSAD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1985-05-05</t>
+          <t>1965-09-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>1965-09-11</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Damascus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>NAME_MISMATCH</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Token order mismatch: Lastname, Firstname vs Firstname, Lastname.</t>
+          <t>Prefix normalized away causing a surname match, but given names belong to completely different people.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nguyễn, Anh</t>
+          <t>García, Ana María</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nguyễn, Anh</t>
+          <t>GARCIA, Luis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1995-02-14</t>
+          <t>García ~ GARCIA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1980-02-14</t>
+          <t>12 April 1982</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>1955-03-20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DOB_MISMATCH_OR_INVALID</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>DOB difference is 15 years, exceeding the 1-year threshold.</t>
+          <t>The DOB disparity is greater than 1 year, triggering a clear mismatch failure despite shared surname.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Smith, John</t>
+          <t>John, Robert</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>IVAN, Robert</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Robert ~ ROBERT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1995-02-14</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>1995-02-14</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Embargoes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>embargo</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EMBARGO_WILDCARD_HIT</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Embargo hit for Iran, but client is located in United Kingdom.</t>
+          <t>Shared middle/given token 'Robert' over-fires while primary names represent different individuals.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Garcia, Elena</t>
+          <t>Tanaka, Kenji</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Garcia, Elena</t>
+          <t>TANAKA, Kenji</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1983-07-12</t>
+          <t>Tanaka ~ TANAKA | Kenji ~ Kenji</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1983-07-12</t>
+          <t>1988-09-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>1988-09-12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Exact name match and valid DOBs; hit_city unavailable - bypassing geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aleppo</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Prefix normalization caused an over-fire on a common surname with distinct given names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Alejandro, Miguel</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ALEX, Miguel</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Miguel ~ MIGUEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1988-10-30</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1988-10-30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Shared given name Miguel triggers engine, but surnames Alejandro and Alex represent different persons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Smith, Jane Adelaide</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1972-11-05</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DOB mismatch of over 10 years confirms different individuals despite shared surname.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>15/04/72</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>15/04/1972</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>DOB and geography are compatible, but different given names make this an over-fire name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>O'Brien, Siobhan</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BRIEN, Michael</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brien ~ BRIEN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Apr 12, 1982</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>12/04/1982</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Apostrophe-split surname matches a different person entirely, resulting in a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Garcia Lopez, Maria</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LOPEZ GARCIA, Carlos</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Lopez ~ LOPEZ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>12 October 1990</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Oct 12, 1990</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>DOB and location match perfectly, but token-order inversion indicates separate individuals. Fired on shared dual surnames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ford, Harrison, Jr.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FORD, HARRISON, III</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ford ~ FORD | Harrison ~ HARRISON</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1942-07-13</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1942-07-13</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Generation suffix mismatch (Jr vs III) indicates distinct individuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Yamamoto, Kenji</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>YAMAMOTO, Kenji</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Yamamoto ~ YAMAMOTO | Kenji ~ Kenji</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1958-11-25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1958-11-20</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Engine false positive due to Asian name-order structure confusion on unrelated records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Garcia Lopez, Maria</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LOPEZ GARCIA, Carlos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Lopez ~ LOPEZ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>12/04/1990</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1990-04-12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Token order permutation and mismatched given names indicate distinct individuals despite shared compound surnames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ivanov, Aleksandr</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ИВАНОВ, Александр</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ivanov ~ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>12.11.1970</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1970-11-15</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Exact name and DOB match under 1 year delta; hit_city unavailable - bypassing geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Garcia Lopez, Maria</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LOPEZ GARCIA, Carlos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Lopez ~ LOPEZ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>12 April 1982</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10 April 1982</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>DOB is valid and geography aligns, but token permutation and different given names result in a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Smith, Jane Adelaide</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Common-name over-match on shared surname Smith, but given names clearly do not match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tanaka, Hiroshi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TANAKA, HIROSHI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tanaka ~ TANAKA | Hiroshi ~ HIROSHI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1988-12-05</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05-12-1988</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Hit city unavailable - bypassing geography granularity. DOB and structured name match are verified completely.  [auto-null: client_city]  [auto-null: client_country]  [auto-null: hit_country]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tanaka, Hiroshi</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TANAKA, Hiroshi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tanaka ~ TANAKA | Hiroshi ~ Hiroshi</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Apr 12, 1992</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1992-04-12</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Hit city is unavailable, bypassing geography cleanly; exact name and matching DOB yield a true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kim, Jong Il</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JONG IL KIM</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kim ~ KIM | Jong ~ JONG | Il ~ IL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Feb 16, 1941</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1941-02-16</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>KP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Structured name normalization yields exact match with matching DOB and geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kim, Jong Il</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JONG IL KIM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Kim, Jong Il ~ JONG IL KIM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1941-02-16</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1941-02-18</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Democratic Peoples Republic of Korea</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Structural reordering matches cleanly with matching dates and equivalent country aliases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kim, Jong Il</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>JONG IL KIM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kim ~ KIM | Jong ~ JONG | Il ~ IL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1978-02-16</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1978-02-16</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Asian name-order reordering resolves successfully with identical DOBs and matching country.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Smyth, James</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SMITH, James</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Smyth ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1970-07-22</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1970-07-22</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>DOB and given names align, but a stark country disparity between the UK and Brazil yields a geographic mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Tanaka, Hiroshi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TANAKA, Hiroshi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tanaka ~ TANAKA | Hiroshi ~ Hiroshi</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22-03-1988</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1988-03-20</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Hit city unavailable - bypassing geography. Names match and DOB is within acceptable tolerance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dubois, Chantal</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DUBOIS, Chantal</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dubois ~ DUBOIS | Chantal ~ Chantal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Paris, FR</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Exact name match, matching birth year, and consistent country geography confirm a true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Prefix-stripped name match fails due to a major 15-year age discrepancy in DOBs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Silva, Joao</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SILVA, Pedro</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Silva ~ SILVA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1983-06-20</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1983-06-20</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Common surname over-fires despite matching DOB and geography, leading to a false name match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Garcia, Maria Isabel</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GARCIA, Maria Isabel</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Maria ~ Maria | Isabel ~ Isabel</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1985-04-15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DOB delta is well under 1 year, geography matches, and names are an exact structured match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Phonetic surname match only, distinct given names prove different individuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>12 April 1982</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>12th April 1982</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Phonetic surname match with umlaut expansion, but given names and individuals do not match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>12 April 1982</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1982-04-12</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cross-script transliteration mismatch despite matching dates and geography tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nguyen, Van Anh</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ANH, NGUYEN</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Nguyen ~ NGUYEN | Van Anh ~ ANH</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1988-12-05</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1988-12-05</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Asian name-order confusion triggers token matches, but structured name order fails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Nguyen, Van Anh</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ANH, NGUYEN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nguyen ~ NGUYEN | Van Anh ~ ANH</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1995-01-22</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1995-01-25</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City</t>
+        </is>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DOB difference is minimal (&lt; 1 year), geography matches completely, and structured names validate successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Garcia, Maria Elena</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GARCIA, Maria Elena</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Maria ~ Maria | Elena ~ Elena</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1990/11/05</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>05/11/1990</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Exact name match, matching DOBs, and consistent geography confirm this is a true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>O'Brien, Siobhan</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BRIEN, Michael</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brien ~ BRIEN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1975-09-14</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1975-09-14</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>DOB and regional proximity are close, but the given names and truncated surnames constitute a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>O'Connor, Liam</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>O'CONNOR, Sean</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>O'Connor ~ O'CONNOR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22nd July 1985</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>22 July 1985</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Shared surname with a different given name results in a false positive name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>O'Connor, Liam</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CONNOR, Michael</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Connor ~ CONNOR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1978-04-30</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1978-04-30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Apostrophe-split surname over-fires on a partial token match for a different individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Smith, J. R.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Smith, J. R. ~ SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1980-05-12</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1980-05-15</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>DOB matches closely and geography aligns, but names represent different individuals due to initial expansion over-fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Smyth, James</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SMITH, James</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Smyth ~ SMITH | James ~ James</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Phonetic surname match with matching geography, but a major 2-year DOB disparity fails the check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ | Dmitri ~ ДМИТРИЙ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1990/07/22</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>22 July 1990</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Exact transliterated name match with identical DOB and matching country; hit_city unavailable - bypassing geography.  [auto-null: hit_city]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kim, Jong Il</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JONG IL KIM</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Kim, Jong Il ~ JONG IL KIM</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1941-02-16</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1941-02-16</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Pyongyang</t>
+        </is>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Exact token and structure match with identical DOB and verified country location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cruz-Ramirez, Elena</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RAMIREZ, Jorge</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ramirez ~ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1995-02-18</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1980-05-12</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Shared compound surname substring, but a major DOB year gap triggers a mismatch failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Smyth, James</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SMITH, James</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Smyth ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1991-09-10</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1991-09-15</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Phonetic name variant and close DOB, but completely divergent country and city records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>12.03.1975</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1975-03-14</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Shared surname root with umlaut normalization, but given names are completely different resulting in a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ford, Harrison, Jr.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FORD, HARRISON, III</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ford, Harrison ~ FORD, HARRISON</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1942-07-13</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Generation suffixes were stripped by the engine, but birth dates show a major year disparity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>O'Brien, Siobhan</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BRIEN, Michael</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brien ~ BRIEN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1992-01-15</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1992-01-15</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cork</t>
+        </is>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Apostrophe-split surname over-fire against a completely different given name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>van der Berg, Jan</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BERG, Klaus</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Berg ~ BERG</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1988-12-01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1988-12-05</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Name and DOB align, but country and city values represent completely different locations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Smith, Jane Adelaide</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1972-11-03</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>DOB and geography are acceptable, but names represent completely different individuals sharing a common surname.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>O'Brien, Siobhan</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BRIEN, Michael</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Brien ~ BRIEN</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1992-03-14</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>14/03/1992</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>DOB matches and given names are close, but client is in Ireland while hit resides in Canada. Geographic mismatch failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Smith, Jane Adelaide</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1982-09-03</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>DOB and geography are compatible, but names represent different individuals sharing a common surname. Fired on surname token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Silva, João Carlos</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SILVA, JOAO CARLOS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Silva ~ SILVA | João ~ JOAO | Carlos ~ CARLOS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1985-03-15</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1985-03-16</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="b">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Exact name and DOB match; hit_city unavailable - bypassing geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ford, Harrison, Jr.</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FORD, HARRISON, III</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ford, Harrison ~ FORD, HARRISON</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1942-07-13</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1955-03-10</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Generation suffix stripped successfully, but dates of birth reveal a major discrepancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>John, Robert</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IVAN, Robert</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Robert ~ ROBERT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Cross-lingual given name synonyms fail to match as the shared middle name fires an over-match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Silva, João Carlos</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SILVA, João Carlos</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Silva ~ SILVA | João ~ João | Carlos ~ Carlos</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1988-07-22</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1988-07-22</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Exact name match, perfectly aligned DOBs, and matching geographic details confirm a true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1978-01-01</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Geography and surname root match, but there is a major year disparity failing the DOB check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Alejandro, Miguel</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ALEX, Miguel</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Miguel ~ MIGUEL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1980-07-22</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1980-07-22</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Shared secondary given name triggers the alert, but primary names indicate separate individuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Smith, Adelaide Jane</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1982-04-12</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1975-09-20</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>DOB and geography are aligned, but the name is an over-match on a shared common surname.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Mueller, Hans Peter</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MUELLER, Hans</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Mueller ~ MUELLER | Hans ~ Hans</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>12-10-1965</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1965-10-12</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>DOB and geography match, but the hit is a partial match missing the client's middle name token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Alejandro, Miguel</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ALEX, Miguel</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Miguel ~ MIGUEL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1980-05-12</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1980-05-12</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>Mexico City</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sanctions</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>non-embargo</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Shared common given name but distinct surnames fail the name match criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Garcia Lopez, Maria</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>LOPEZ GARCIA, Carlos</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Lopez ~ LOPEZ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1990/02/20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1990/02/21</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>GEOGRAPHIC_MISMATCH</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Name and DOB match, but client country (Spain) differs from hit country (Mexico).</t>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Names share tokens and DOB is aligned, but distinct countries result in a geographic mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Smith, J. R.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Smith, J. R. ~ SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1985-06-12</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1985-06-12</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Initials expanded into a different individual despite matching surname, resulting in a false name match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>03-03-1965</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1965-03-05</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Shared German surname variant but given names differ, resulting in a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nguyen, Van Anh</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ANH, NGUYEN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Nguyen ~ NGUYEN | Van Anh ~ ANH</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1995-07-20</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1995-07-21</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="b">
+        <v>1</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Token-order normalization handles Asian name structure correctly, hit_city unavailable - bypassing geography.  [auto-null: hit_city]  [auto-null: client_city]  [auto-null: client_country]  [auto-null: hit_country]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Müller, Hans Peter</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>15/04/82</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>15.04.1982</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>DOB and locations match despite transliteration variations, and names align under normalization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Müller, Hans Peter</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MUELLER, Hans</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER | Hans ~ Hans</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>12.03.1978</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>15-03-1978</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J91" t="b">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>DOB falls within acceptable range, geography matches across spellings, and name tokens align closely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1982-11-20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Names match via transliteration, but a major year disparity triggers a DOB mismatch failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Patel, Priya</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PATEL, Priya</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Patel ~ PATEL | Priya ~ Priya</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Apr 12, 1992</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1992-04-12</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Exact name, normalized dates, and matching Indian geography validate a true match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Alejandro, Miguel</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ALEX, Miguel</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Miguel ~ MIGUEL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1980-10-10</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Engine fired on a shared common given name while surnames are completely different.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Garcia, Elena Maria</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GARCIA, Elena Maria</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Elena ~ Elena | Maria ~ Maria</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>14-06-1988</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>14-06-1988</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J95" t="b">
+        <v>1</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Exact name match, identical DOB, and matching country and city confirm a true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Yamamoto, Kenji</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>YAMAMOTO, Kenji</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Yamamoto ~ YAMAMOTO | Kenji ~ KENJ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="b">
+        <v>1</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_MISSING_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Exact name and DOB match; hit_city unavailable - bypassing geography.  [auto-null: client_dob]  [auto-null: hit_dob]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11 September 1965</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>12 Sep 1965</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Aleppo</t>
+        </is>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Prefix normalization causes a common surname hit, but given names and identities do not match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>O'Brien, Siobhan</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BRIEN, Michael</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Brien ~ BRIEN</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1978-05-30</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1978-05-30</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Apostrophe-split surname over-fires the engine, yet the given names do not correspond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Geography and partial name root match, but a 5-year gap triggers a DOB mismatch failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1990.05.20</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1990-05-20</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Saint Petersburg</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Names match across transliteration and DOB matches, but client and hit cities are clearly divergent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Haddad, Karim</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KARIM HADDAD</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Haddad, Karim ~ KARIM HADDAD</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1992/05/11</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1992-05-11</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Beirut</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Tripoli</t>
+        </is>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Geography and DOB are fine, but token order and full identity check indicate a false positive from a reversed index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Schmidt, Anna</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SCHMIDT, Anna</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Schmidt ~ SCHMIDT | Anna ~ ANNA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1995-12-05</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1995-12-06</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="J102" t="b">
+        <v>1</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Exact name match with a minimal one-day DOB variance and matching country validates the true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Schmidt, Hans Jürgen</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SCHMIDT, Hans Juergen</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Schmidt ~ SCHMIDT | Hans ~ Hans | Jürgen ~ Juergen</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1990.05.20</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1990/05/20</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="J103" t="b">
+        <v>1</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Dates align perfectly, geographic locations match across aliases, and name tokens correspond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1975.05.20</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Cross-script transliteration mismatch representing distinct persons despite shared surname.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>John, Robert</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IVAN, Robert</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Robert ~ ROBERT</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10/05/1995</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>10/05/1995</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Cross-lingual given name differences and distinct primary names cause a name mismatch despite matching DOB and geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Smith, Jane Adelaide</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1972-11-05</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>DOB and geography align, but names represent completely different individuals sharing a common surname.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>15.04.1975</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>10-11-1960</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Major DOB disparity exceeding one year triggers a mismatch failure despite surname phonetic overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Nguyen, Van Anh</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ANH, NGUYEN</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Nguyen ~ NGUYEN | Van Anh ~ ANH</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Name tokens overlap due to reverse order, but a 3-year DOB gap fails the check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ | Dmitri ~ ДМИТРИЙ</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>12-11-1970</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1970-11-10</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J109" t="b">
+        <v>1</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Cross-script transliteration matches correctly with valid DOB and matching locations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1965-09-10</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>DOB and surname match, but disparate countries indicate a geographic mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>15-08-1970</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>15.08.1970</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>DOB and geography are compatible, but the given names do not match, indicating distinct persons with similar surnames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tan, Wei Ling</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TAN, Wei Ling</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tan ~ TAN | Wei ~ Wei | Ling ~ Ling</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Apr 12, 1992</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1992-04-12</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="b">
+        <v>1</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Hit city unavailable bypassing geography city check; names and DOBs match perfectly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>O'Connor, Patrick</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CONNOR, Michael</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Connor ~ CONNOR</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1975-08-19</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1975-08-19</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="J113" t="b">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>DOB and geography match, but the apostrophe-split surname over-fired on different given names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Token order permutation and script mismatch cause a name mismatch despite matching birth years and geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>García, Ana María</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GARCIA, Luis</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>García ~ GARCIA</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1990-05-15</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1985-11-22</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J115" t="b">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Shared common surname but significant date of birth disparity triggers a mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Garcia Lopez, Maria</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GARCIA LOPEZ, Maria</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Lopez ~ LOPEZ | Maria ~ Maria</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>12 October 1990</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>12-10-1990</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J116" t="b">
+        <v>1</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Exact structured name match with matching DOB and geographical context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>12 October 1975</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12.10.1975</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="J117" t="b">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>DOB and geography are valid, but the given names differ, resulting in a name mismatch for unrelated individuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Smith, Jane Adelaide</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1982-11-05</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>DOB is acceptable and geography matches, but names belong to completely different individuals sharing a common surname.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>O'Connor, Liam</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>O'CONNOR, Liam</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>O'Connor ~ O'CONNOR | Liam ~ Liam</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1992-06-14</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1992-06-14</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="J119" t="b">
+        <v>1</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Exact name match, identical date of birth, and matching Irish geography confirm a true alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Ford, Harrison, Jr.</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>FORD, HARRISON, III</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ford, Harrison ~ FORD, HARRISON</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1942-07-13</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1942-07-13</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="J120" t="b">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Generation markers stripped by the engine, but Jr versus III confirms distinct family members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ivanov, Aleksandr</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ИВАНОВ, Александр</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ivanov ~ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1990.05.20</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1990-05-22</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J121" t="b">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Minor DOB variance is well under 1 year, and names/geography match across transliteration scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Wong, Li Wei</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>WONG, Wei</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Wong ~ WONG | Wei ~ Wei</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>05/12/1995</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1995-12-05</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J122" t="b">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Name tokens overlap partially, but country and city records indicate entirely distinct profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Müller, Hans</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MUELLER, Josef</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Müller ~ MUELLER</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>15.03.1975</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>15-03-1975</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="J123" t="b">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Shared common surname with umlaut normalization, but distinct given names yield a false positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ivanov, Aleksandr</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ИВАНОВ, Александр</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ivanov ~ ИВАНОВ | Aleksandr ~ Александр</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1978-06-20</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>20-06-1978</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="J124" t="b">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Exact name and DOB match with consistent Russian geography across scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1965-09-12</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="J125" t="b">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Prefix normalization triggered an engine over-fire on the surname, but given names clearly mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Nguyen, Van Anh</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NGUYEN, Van Anh</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Nguyen ~ NGUYEN | Van ~ Van | Anh ~ Anh</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1988.11.04</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>04/11/1988</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="b">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Exact name and DOB match; hit_city unavailable - bypassing geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Smith, John Robert</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SMITH, John Robert</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH | John ~ John | Robert ~ Robert</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>12-09-1978</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1978-09-12</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="b">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>DOB and country match while hit_city is missing, allowing a successful match decision.  [auto-null: client_city]  [auto-null: hit_country]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Smith, J. R.</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Smith, J. R. ~ SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1975-06-20</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1975-06-20</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J128" t="b">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Initials match the expanded name, but conflicting cities within the USA break geography consistency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ho, Wei Ming</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HO CHI MINH</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ho ~ HO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1945-08-19</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>19.05.1890</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J129" t="b">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Two-letter surname over-fires on a historical figure and the DOB fails due to a large gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>De Silva, Marcus</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DE SILVA, Marcus</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>De Silva ~ DE SILVA | Marcus ~ Marcus</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1979-11-05</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1979-11-06</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="J130" t="b">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Names, DOB delta under 1 year, and geography all perfectly match for a true positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Garcia Lopez, Maria</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LOPEZ GARCIA, Carlos</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Garcia ~ GARCIA | Lopez ~ LOPEZ</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>15/04/1990</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>15-04-1990</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="J131" t="b">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Shared surnames in reordered token sequence fail strict structure and identity checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Smith, J. R.</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Smith, J. R. ~ SMITH, JOHN ROBERT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1985-04-12</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1985-04-15</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J132" t="b">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>DOB matches and geography aligns, but initials versus full expanded names constitute a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Tanaka, Hiroshi</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TANAKA, Hiroshi</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tanaka ~ TANAKA | Hiroshi ~ Hiroshi</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1965.11.30</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>30/11/1965</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="b">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Hit city unavailable - bypassing geography. Exact name and matching DOB confirm true match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>John, Robert</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IVAN, Robert</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Robert ~ ROBERT</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1981-12-01</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1981-12-05</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J134" t="b">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>DOB and geography align, but cross-lingual given names result in a name mismatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Aleppo</t>
+        </is>
+      </c>
+      <c r="J135" t="b">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Major calendar year disparity exceeding one year triggers a DOB mismatch failure. Name shares a truncated root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="J136" t="b">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Both records provide year-level identifiers showing a 15-year gap, failing the DOB check despite matching geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Petrov, Dmitri</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ДМИТРИЙ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Petrov ~ ПЕТРОВ</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1990-12-01</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1990-12-01</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Saint Petersburg</t>
+        </is>
+      </c>
+      <c r="J137" t="b">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_COUNTRY_MATCH</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Exact structured name match with matching DOB and consistent cross-lingual geography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>de la Torre, F.</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TORRE, FERNANDO</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>de la Torre, F. ~ TORRE, FERNANDO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1978-06-15</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1978-06-10</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="b">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>EXACT_NAME_MATCH_DOB_OK_CITY_MISSING</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>DOB matches within tolerance and hit_city is unavailable, bypassing geography check to confirm the match.  [auto-null: hit_city]  [auto-null: client_city]  [auto-null: client_country]  [auto-null: hit_country]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Nguyen, Van Anh</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NGUYEN, Hoang</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Nguyen ~ NGUYEN</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1995-12-01</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1995-12-01</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
+      <c r="J139" t="b">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Shared common Vietnamese surname over-fires while given names are clearly different.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Al-Assad, Bashar</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ASSAD, Batyr</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Al-Assad ~ ASSAD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1965-09-11</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Aleppo</t>
+        </is>
+      </c>
+      <c r="J140" t="b">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>DOB_MISMATCH_OR_INVALID</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Significant year gap in DOB values fails the validation check, confirming distinct individuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Smith, Adelaide Jane</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SMITH, Robert</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Smith ~ SMITH</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>15/04/1982</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1982-04-12</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="J141" t="b">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>NAME_MISMATCH</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>DOB is acceptable, but names represent completely different individuals sharing a common surname.</t>
         </is>
       </c>
     </row>
